--- a/Excels/#Trigger.xlsx
+++ b/Excels/#Trigger.xlsx
@@ -32,10 +32,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>asset_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>event_enemy_death_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -68,6 +64,10 @@
   </si>
   <si>
     <t>event_enemy_death_1</t>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -432,13 +432,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -452,7 +452,7 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -462,24 +462,24 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
